--- a/tests/fixtures/2016-2025 SDN Overview Data.xlsx
+++ b/tests/fixtures/2016-2025 SDN Overview Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
   <si>
     <t>Country</t>
   </si>
@@ -88,7 +88,172 @@
     <t>Sudan</t>
   </si>
   <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>SDN</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>104</t>
   </si>
 </sst>
 </file>
@@ -501,65 +666,65 @@
       <c r="B2">
         <v>2025</v>
       </c>
-      <c r="C2">
-        <v>58</v>
-      </c>
-      <c r="D2">
-        <v>59</v>
-      </c>
-      <c r="E2">
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="F2">
-        <v>121</v>
-      </c>
-      <c r="G2">
-        <v>51</v>
-      </c>
-      <c r="I2">
-        <v>63</v>
-      </c>
-      <c r="J2">
-        <v>49</v>
-      </c>
-      <c r="K2">
-        <v>40</v>
-      </c>
-      <c r="L2">
-        <v>51</v>
-      </c>
-      <c r="M2">
-        <v>11</v>
-      </c>
-      <c r="N2">
-        <v>15</v>
-      </c>
-      <c r="O2">
-        <v>27</v>
-      </c>
-      <c r="P2">
-        <v>12</v>
-      </c>
-      <c r="Q2">
-        <v>14</v>
-      </c>
-      <c r="R2">
-        <v>11</v>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2">
-        <v>211</v>
-      </c>
-      <c r="U2">
-        <v>179</v>
-      </c>
-      <c r="V2">
-        <v>104</v>
-      </c>
-      <c r="W2">
-        <v>3</v>
+        <v>72</v>
+      </c>
+      <c r="T2" t="s">
+        <v>73</v>
+      </c>
+      <c r="U2" t="s">
+        <v>76</v>
+      </c>
+      <c r="V2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -569,68 +734,68 @@
       <c r="B3">
         <v>2024</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" t="s">
+        <v>74</v>
+      </c>
+      <c r="U3" t="s">
         <v>77</v>
       </c>
-      <c r="D3">
-        <v>95</v>
-      </c>
-      <c r="E3">
-        <v>45</v>
-      </c>
-      <c r="F3">
-        <v>264</v>
-      </c>
-      <c r="G3">
-        <v>67</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>71</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>38</v>
-      </c>
-      <c r="L3">
-        <v>67</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-      <c r="N3">
-        <v>23</v>
-      </c>
-      <c r="O3">
-        <v>72</v>
-      </c>
-      <c r="P3">
-        <v>47</v>
-      </c>
-      <c r="Q3">
-        <v>27</v>
-      </c>
-      <c r="R3">
+      <c r="V3" t="s">
         <v>26</v>
       </c>
-      <c r="S3" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3">
-        <v>186</v>
-      </c>
-      <c r="U3">
-        <v>115</v>
-      </c>
-      <c r="V3">
-        <v>40</v>
-      </c>
-      <c r="W3">
-        <v>1</v>
+      <c r="W3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -640,62 +805,62 @@
       <c r="B4">
         <v>2023</v>
       </c>
-      <c r="C4">
-        <v>40</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
-      </c>
-      <c r="F4">
-        <v>290</v>
-      </c>
-      <c r="G4">
-        <v>120</v>
-      </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
-      <c r="I4">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="J4">
-        <v>8</v>
-      </c>
-      <c r="K4">
-        <v>19</v>
-      </c>
-      <c r="L4">
-        <v>56</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <v>45</v>
-      </c>
-      <c r="O4">
-        <v>68</v>
-      </c>
-      <c r="P4">
-        <v>77</v>
-      </c>
-      <c r="Q4">
-        <v>22</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R4" t="s">
+        <v>30</v>
       </c>
       <c r="S4" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4">
-        <v>114</v>
-      </c>
-      <c r="U4">
-        <v>50</v>
+        <v>72</v>
+      </c>
+      <c r="T4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -705,62 +870,62 @@
       <c r="B5">
         <v>2022</v>
       </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>64</v>
-      </c>
-      <c r="G5">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>13</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-      <c r="N5">
-        <v>13</v>
-      </c>
-      <c r="O5">
-        <v>14</v>
-      </c>
-      <c r="P5">
-        <v>9</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
+        <v>56</v>
       </c>
       <c r="S5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5">
-        <v>4</v>
-      </c>
-      <c r="U5">
-        <v>21</v>
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>52</v>
+      </c>
+      <c r="U5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -770,56 +935,56 @@
       <c r="B6">
         <v>2021</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>61</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-      <c r="N6">
-        <v>25</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>8</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" t="s">
+        <v>56</v>
       </c>
       <c r="S6" t="s">
-        <v>24</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
-      </c>
-      <c r="U6">
-        <v>12</v>
+        <v>72</v>
+      </c>
+      <c r="T6" t="s">
+        <v>31</v>
+      </c>
+      <c r="U6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -829,56 +994,56 @@
       <c r="B7">
         <v>2020</v>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7" t="s">
+        <v>56</v>
       </c>
       <c r="S7" t="s">
-        <v>24</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="U7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -888,41 +1053,41 @@
       <c r="B8">
         <v>2019</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>35</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>5</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>11</v>
-      </c>
-      <c r="O8">
-        <v>3</v>
-      </c>
-      <c r="P8">
-        <v>3</v>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" t="s">
+        <v>29</v>
       </c>
       <c r="S8" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -932,26 +1097,26 @@
       <c r="B9">
         <v>2018</v>
       </c>
-      <c r="F9">
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" t="s">
+        <v>56</v>
       </c>
       <c r="S9" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -961,38 +1126,38 @@
       <c r="B10">
         <v>2017</v>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P10" t="s">
+        <v>56</v>
       </c>
       <c r="S10" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1002,38 +1167,38 @@
       <c r="B11">
         <v>2016</v>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>4</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" t="s">
+        <v>56</v>
+      </c>
+      <c r="P11" t="s">
+        <v>56</v>
       </c>
       <c r="S11" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
